--- a/data/trans_orig/IP22_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP22_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17814</t>
+          <t>18110</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8580</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>19579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18458</t>
+          <t>18698</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33505</t>
+          <t>33379</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73053</t>
+          <t>72757</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83559</t>
+          <t>83659</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67222</t>
+          <t>67266</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78635</t>
+          <t>78265</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144207</t>
+          <t>144333</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159254</t>
+          <t>159014</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74957</t>
+          <t>75521</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101072</t>
+          <t>102291</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89824</t>
+          <t>91108</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>119371</t>
+          <t>118172</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172147</t>
+          <t>170206</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>214916</t>
+          <t>210192</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>315015</t>
+          <t>313796</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>341130</t>
+          <t>340566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>357620</t>
+          <t>358819</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>387167</t>
+          <t>385883</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>678162</t>
+          <t>682886</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>720931</t>
+          <t>722872</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24914</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41707</t>
+          <t>41614</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31986</t>
+          <t>31578</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49017</t>
+          <t>49134</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59701</t>
+          <t>61669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84157</t>
+          <t>85505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>132359</t>
+          <t>132452</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149152</t>
+          <t>149758</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>109121</t>
+          <t>109004</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>126152</t>
+          <t>126560</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>248048</t>
+          <t>246700</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>272504</t>
+          <t>270536</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,44%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114820</t>
+          <t>114811</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>148284</t>
+          <t>148370</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>140230</t>
+          <t>139964</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>176869</t>
+          <t>176140</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>264501</t>
+          <t>265351</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>311355</t>
+          <t>317361</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>532737</t>
+          <t>532651</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>566201</t>
+          <t>566210</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>545105</t>
+          <t>545834</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>581744</t>
+          <t>582010</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1091640</t>
+          <t>1085634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1138494</t>
+          <t>1137644</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14997</t>
+          <t>14683</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28462</t>
+          <t>27940</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19670</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34094</t>
+          <t>34259</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37811</t>
+          <t>39024</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57515</t>
+          <t>58657</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63907</t>
+          <t>64429</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77372</t>
+          <t>77686</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51241</t>
+          <t>51076</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65665</t>
+          <t>65291</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>120188</t>
+          <t>119046</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139892</t>
+          <t>138679</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,04%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89971</t>
+          <t>90116</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>119906</t>
+          <t>120776</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121651</t>
+          <t>122265</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>155614</t>
+          <t>155131</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>220070</t>
+          <t>219341</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>265884</t>
+          <t>264791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>331659</t>
+          <t>330789</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>361594</t>
+          <t>361449</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>336533</t>
+          <t>337016</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370496</t>
+          <t>369882</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>677828</t>
+          <t>678921</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>723642</t>
+          <t>724371</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32812</t>
+          <t>32365</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51190</t>
+          <t>51284</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33464</t>
+          <t>33760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51182</t>
+          <t>52256</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71252</t>
+          <t>71700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98913</t>
+          <t>97399</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115622</t>
+          <t>115528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134000</t>
+          <t>134447</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121046</t>
+          <t>119972</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138764</t>
+          <t>138468</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>240128</t>
+          <t>241642</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>267789</t>
+          <t>267341</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>149607</t>
+          <t>148063</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187162</t>
+          <t>187006</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>187134</t>
+          <t>184231</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>227102</t>
+          <t>227548</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>347667</t>
+          <t>350714</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>403890</t>
+          <t>403797</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>523584</t>
+          <t>523740</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>561139</t>
+          <t>562683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>522608</t>
+          <t>522162</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>562576</t>
+          <t>565479</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1056566</t>
+          <t>1056659</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1112789</t>
+          <t>1109742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,99%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16236</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13018</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12478</t>
+          <t>13157</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25742</t>
+          <t>25566</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>43277</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52906</t>
+          <t>53459</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55596</t>
+          <t>55669</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64182</t>
+          <t>64515</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102251</t>
+          <t>102427</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115515</t>
+          <t>114836</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67755</t>
+          <t>67844</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>94294</t>
+          <t>95254</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68959</t>
+          <t>70381</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96280</t>
+          <t>98279</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>144478</t>
+          <t>145418</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>181942</t>
+          <t>182428</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,98%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>377996</t>
+          <t>377036</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404535</t>
+          <t>404446</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>392455</t>
+          <t>390456</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>419776</t>
+          <t>418354</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>779083</t>
+          <t>778597</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>816547</t>
+          <t>815607</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26144</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42807</t>
+          <t>41992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25537</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43523</t>
+          <t>43163</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56524</t>
+          <t>55871</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80935</t>
+          <t>80435</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>129896</t>
+          <t>130711</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146559</t>
+          <t>147381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143154</t>
+          <t>143514</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161140</t>
+          <t>160733</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>278444</t>
+          <t>278944</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>302855</t>
+          <t>303508</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,45%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>109625</t>
+          <t>108595</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>143203</t>
+          <t>140126</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108303</t>
+          <t>108277</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142659</t>
+          <t>141691</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>227897</t>
+          <t>224244</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>273282</t>
+          <t>271598</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>561168</t>
+          <t>564245</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>594746</t>
+          <t>595776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>601367</t>
+          <t>602335</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>635723</t>
+          <t>635749</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1175115</t>
+          <t>1176799</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1220500</t>
+          <t>1224153</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26488</t>
+          <t>25420</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18397</t>
+          <t>18456</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13299</t>
+          <t>13595</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37105</t>
+          <t>37221</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28190</t>
+          <t>29258</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50721</t>
+          <t>51032</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43607</t>
+          <t>43548</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55436</t>
+          <t>55523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79577</t>
+          <t>79461</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103383</t>
+          <t>103087</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49576</t>
+          <t>48939</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77803</t>
+          <t>77045</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58717</t>
+          <t>58320</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89012</t>
+          <t>89869</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116270</t>
+          <t>116280</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>157223</t>
+          <t>158421</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>381168</t>
+          <t>381926</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>409395</t>
+          <t>410032</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>427607</t>
+          <t>426750</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>457902</t>
+          <t>458299</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>818367</t>
+          <t>817169</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>859320</t>
+          <t>859310</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>22913</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38267</t>
+          <t>39636</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>23358</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42427</t>
+          <t>43505</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50125</t>
+          <t>50415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75013</t>
+          <t>75067</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>111284</t>
+          <t>109915</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128178</t>
+          <t>126638</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140922</t>
+          <t>139844</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160120</t>
+          <t>159991</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>257887</t>
+          <t>257833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>282775</t>
+          <t>282485</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85684</t>
+          <t>85213</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125508</t>
+          <t>126818</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99644</t>
+          <t>99617</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>138030</t>
+          <t>135313</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>194441</t>
+          <t>192871</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>253286</t>
+          <t>250613</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>537692</t>
+          <t>536382</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>577516</t>
+          <t>577987</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>623942</t>
+          <t>626659</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>662328</t>
+          <t>662355</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1171886</t>
+          <t>1174559</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1230731</t>
+          <t>1232301</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP22_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13559</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8741</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19820</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15,61%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,07%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>22,82%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>12081</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7208</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18110</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7952</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18602</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>13,29%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,93%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>13559</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8580</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>19579</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>15,61%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18698</t>
+          <t>18381</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33379</t>
+          <t>34155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>73286</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>67025</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>78104</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>84,39%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77,18%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89,93%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>78786</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>72757</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>83659</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>72265</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>82915</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>86,71%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>80,07%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,07%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>73286</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>67266</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>78265</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>84,39%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144333</t>
+          <t>143557</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159014</t>
+          <t>159331</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,66%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>103582</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>90665</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>119835</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21,72%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>19,01%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25,12%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>87082</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>75521</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>102291</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>75789</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>101120</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>20,93%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,15%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>103582</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>91108</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>118172</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>21,72%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>170206</t>
+          <t>170297</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>210192</t>
+          <t>210187</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>373409</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>357156</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>386326</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>78,28%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>80,99%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>494</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>329005</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>313796</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>340566</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>314967</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>340298</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>79,07%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,42%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,85%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>373409</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>358819</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>385883</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>78,28%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>682886</t>
+          <t>682891</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>722872</t>
+          <t>722781</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>39888</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>31735</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>49134</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>25,22%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20,07%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>31,07%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>32498</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>24308</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>41614</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>25199</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>42364</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>18,67%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>39888</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>31578</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>49134</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>25,22%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61669</t>
+          <t>61277</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85505</t>
+          <t>85632</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>118250</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>109004</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>126403</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>74,78%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>68,93%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>79,93%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>141568</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>132452</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>149758</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>148867</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>81,33%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>76,09%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86,04%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>118250</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>109004</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>126560</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>74,78%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>246700</t>
+          <t>246573</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>270536</t>
+          <t>270928</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,55%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>157029</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>139634</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>174556</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21,75%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24,18%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>131661</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>114811</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>148370</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>116201</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>149172</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>19,33%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>157029</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>139964</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>176140</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>21,75%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>265351</t>
+          <t>262134</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>317361</t>
+          <t>313339</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>564945</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>547418</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>582340</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>78,25%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>75,82%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>80,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>817</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>549360</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>532651</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>566210</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>531849</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>564820</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>80,67%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>78,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>83,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>564945</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>545834</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>582010</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>78,25%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1085634</t>
+          <t>1089656</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1137644</t>
+          <t>1140861</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,32%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26828</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19868</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34511</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>31,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>23,28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>40,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>21111</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14683</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>27940</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14654</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>27795</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>22,86%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>26828</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>20044</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>34259</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>31,44%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39024</t>
+          <t>37750</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58657</t>
+          <t>58436</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>58507</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>50824</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>65467</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>68,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>59,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>76,72%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>71258</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>64429</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>77686</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>64574</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>77715</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>77,14%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>69,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>58507</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>51076</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>65291</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>68,56%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>119046</t>
+          <t>119267</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>138679</t>
+          <t>139953</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,76%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>85335</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>85335</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>85335</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>85335</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>85335</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>85335</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>137670</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>120088</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>154766</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>24,4%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>31,45%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>105050</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>90116</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>120776</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>90227</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>120700</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>23,26%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>19,96%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,75%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>137670</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>122265</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>155131</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>27,97%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>219341</t>
+          <t>220936</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>264791</t>
+          <t>264765</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>354477</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>337381</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>372059</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>72,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>68,55%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>75,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>501</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>346515</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>330789</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>361449</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>330865</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>361338</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>76,74%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,25%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>80,04%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>354477</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>337016</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>369882</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>72,03%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>678921</t>
+          <t>678947</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>724371</t>
+          <t>722776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,59%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492147</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492147</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492147</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>451565</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>451565</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>451565</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492147</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492147</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42320</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33068</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>52747</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>24,57%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>19,2%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>30,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>41657</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>32365</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>51284</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>33139</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>51414</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>24,97%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>42320</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>33760</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>52256</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>24,57%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71700</t>
+          <t>71178</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97399</t>
+          <t>99003</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>129908</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>119481</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>139160</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>75,43%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>69,37%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>80,8%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>125155</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>115528</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>134447</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>115398</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>133673</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>75,03%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>69,26%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>80,6%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>129908</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>119972</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>138468</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>75,43%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>241642</t>
+          <t>240038</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>267341</t>
+          <t>267863</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,01%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>206817</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>186823</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>227905</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>27,59%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>24,92%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>30,4%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>167818</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>148063</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>187006</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>151095</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>186466</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>23,61%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20,83%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>26,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>206817</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>184231</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>227548</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>27,59%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>350714</t>
+          <t>345936</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>403797</t>
+          <t>401907</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>776</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>542893</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>521805</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>562887</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>72,41%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>69,6%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>75,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>781</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>542928</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>523740</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>562683</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>524280</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>559651</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>76,39%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>73,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>79,17%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>542893</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>522162</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>565479</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>72,41%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1056659</t>
+          <t>1058549</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1109742</t>
+          <t>1114520</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>76,31%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1069</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>749710</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>749710</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>749710</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>710746</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>710746</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>710746</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1069</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>749710</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>749710</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>749710</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8067</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4231</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13168</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,76%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,17%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>19,19%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10284</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5919</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16101</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6233</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>16133</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>17,32%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,97%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>27,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8067</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4099</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12945</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,76%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13157</t>
+          <t>13076</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25566</t>
+          <t>25763</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60547</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>55446</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>64383</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>80,81%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,83%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>49094</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>43277</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>53459</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>43245</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>53145</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>82,68%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>72,88%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>90,03%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60547</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>55669</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>64515</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,24%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102427</t>
+          <t>102230</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>114836</t>
+          <t>114917</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>82341</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>69452</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>97967</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,21%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,05%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>80078</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>67844</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>95254</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>67032</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>93290</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>16,96%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14,36%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,17%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>82341</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>70381</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>98279</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>16,85%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>145418</t>
+          <t>144934</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>182428</t>
+          <t>184693</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>406394</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>390768</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>419283</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>83,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,95%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85,79%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>589</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>392212</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>377036</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>404446</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>379000</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>405258</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>83,04%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,83%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>85,64%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>406394</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>390456</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>418354</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>83,15%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>778597</t>
+          <t>776332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>815607</t>
+          <t>816091</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,92%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34120</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26089</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>43711</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18,28%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13,98%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23,42%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>33722</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>25322</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>41992</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>26092</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>42374</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>19,53%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,66%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>34120</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>25944</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>43163</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>18,28%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55871</t>
+          <t>54914</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80435</t>
+          <t>78801</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>152557</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>142966</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>160588</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>81,72%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>76,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>86,02%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>138981</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>130711</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>147381</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>130329</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>146611</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>80,47%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,69%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,34%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>152557</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>143514</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>160733</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>81,72%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>278944</t>
+          <t>280578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>303508</t>
+          <t>304465</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,72%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>186677</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>186677</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>186677</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>186677</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>186677</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>186677</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>124527</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>107955</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>142338</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,13%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>124084</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>108595</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>140126</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>108859</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>140183</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>17,62%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>124527</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>108277</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>141691</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>224244</t>
+          <t>226452</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>271598</t>
+          <t>272633</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>619499</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>601688</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>636071</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>80,87%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>867</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>580287</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>564245</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>595776</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>564188</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>595512</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>82,38%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>80,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>84,58%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>886</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>619499</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>602335</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>635749</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>83,26%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1176799</t>
+          <t>1175764</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1224153</t>
+          <t>1221945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744026</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744026</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744026</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744026</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744026</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744026</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9793</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5736</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16524</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,26%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29,13%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10660</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3646</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>25420</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19,5%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>46,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11373</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18456</t>
+          <t>10012</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>22033</t>
+          <t>15577</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13595</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37221</t>
+          <t>24012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>46939</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>40208</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>50996</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82,74%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>70,87%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>44018</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>29258</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>51032</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>80,5%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>53,51%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50631</t>
+          <t>40974</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43548</t>
+          <t>36746</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55523</t>
+          <t>43835</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>94649</t>
+          <t>87913</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79461</t>
+          <t>79478</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103087</t>
+          <t>93404</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>66973</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>53849</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>82600</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,36%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>62926</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>48939</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>77045</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13,71%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,66%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>73221</t>
+          <t>60045</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58320</t>
+          <t>48065</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89869</t>
+          <t>72504</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>136147</t>
+          <t>127018</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116280</t>
+          <t>107331</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>158421</t>
+          <t>145392</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>408705</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>393078</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>421829</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>549</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>396045</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>381926</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>410032</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>86,29%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>562</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>443398</t>
+          <t>370861</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>426750</t>
+          <t>358402</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>458299</t>
+          <t>382841</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>839443</t>
+          <t>779566</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>817169</t>
+          <t>761192</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>859310</t>
+          <t>799253</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,16%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>641</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>458971</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>458971</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>458971</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>430906</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>430906</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>430906</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>975590</t>
+          <t>906584</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>975590</t>
+          <t>906584</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>975590</t>
+          <t>906584</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28856</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20952</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39242</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17,13%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,44%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>29649</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>22913</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>39636</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,83%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>32244</t>
+          <t>29959</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23358</t>
+          <t>22761</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43505</t>
+          <t>38904</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>61893</t>
+          <t>58814</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50415</t>
+          <t>48014</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75067</t>
+          <t>72100</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>139563</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>129177</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>147467</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>82,87%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>76,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>87,56%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>119902</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>109915</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>126638</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>80,17%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>73,5%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>84,68%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>151105</t>
+          <t>120017</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139844</t>
+          <t>111072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159991</t>
+          <t>127215</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>271007</t>
+          <t>259581</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>257833</t>
+          <t>246295</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>282485</t>
+          <t>270381</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,92%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>105622</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>90588</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>125160</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15,07%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,93%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>103235</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>85213</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>126818</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>15,57%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,85%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,12%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>116838</t>
+          <t>95787</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99617</t>
+          <t>80897</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>135313</t>
+          <t>111000</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>220073</t>
+          <t>201409</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>192871</t>
+          <t>177422</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>250613</t>
+          <t>226078</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>595207</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>575669</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>610241</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>84,93%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>82,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>87,07%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>791</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>559965</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>536382</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>577987</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>84,43%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>80,88%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,15%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>645134</t>
+          <t>531853</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>626659</t>
+          <t>516640</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>662355</t>
+          <t>546743</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1205099</t>
+          <t>1127060</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1174559</t>
+          <t>1102391</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1232301</t>
+          <t>1151047</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,64%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>940</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663200</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663200</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663200</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>627640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>627640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>627640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1425172</t>
+          <t>1328469</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1425172</t>
+          <t>1328469</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1425172</t>
+          <t>1328469</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
